--- a/www/download/IND.surplus_value.empe_hs.r.pc.rpA1.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>0.103852801731992</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>0.0663552902016546</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>0.0930865112559793</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>0.0904929248590522</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>0.0301022454012259</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>0.0914738445369334</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>0.120350316793043</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>0.0887629395174372</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>0.0276585002063658</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>-0.122662514654129</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-16.98</t>
+          <t>-0.169756072777145</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-0.142405662980378</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-14.99</t>
+          <t>-0.149850187330357</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-0.062583100798062</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.0205917729561027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-36.7</t>
+          <t>-0.367022175374672</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-34.28</t>
+          <t>-0.342763906280861</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-0.206908767314119</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-0.209455254674641</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-20.61</t>
+          <t>-0.206077291792846</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-14.99</t>
+          <t>-0.149909441763674</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-15.06</t>
+          <t>-0.150557573606853</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-0.157513892641847</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-19.21</t>
+          <t>-0.192075452409028</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-24.69</t>
+          <t>-0.24689941789194</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-0.256655472249624</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-27.55</t>
+          <t>-0.275527927979466</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-27.76</t>
+          <t>-0.277585939089733</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-26.01</t>
+          <t>-0.260091092426949</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-20.02</t>
+          <t>-0.200196380331393</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-47.33</t>
+          <t>-0.47331124432412</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-47.98</t>
+          <t>-0.479845159449395</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-45.1</t>
+          <t>-0.450976641209856</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-0.44428503873007</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-49.14</t>
+          <t>-0.491375344249931</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-0.497490704568777</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-52.33</t>
+          <t>-0.523259981487791</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-55.52</t>
+          <t>-0.555181912630906</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-60.98</t>
+          <t>-0.609780524701421</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.27</t>
+          <t>-0.652650031460666</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-64.75</t>
+          <t>-0.647462819394403</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-64.27</t>
+          <t>-0.642661392472699</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-62.1</t>
+          <t>-0.621018848515743</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-56.52</t>
+          <t>-0.565239399703762</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-58.53</t>
+          <t>-0.585252708258775</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>134.26</t>
+          <t>1.3425865793294</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>1.71292922615428</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>209.02</t>
+          <t>2.09017717398684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>116.87</t>
+          <t>1.16866679801644</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>132.63</t>
+          <t>1.32634397236754</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>1.26704226386536</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>118.38</t>
+          <t>1.18378460230484</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>117.43</t>
+          <t>1.17430339365031</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>1.81001729184341</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>1.29899670450351</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>135.26</t>
+          <t>1.35259090592564</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>144.54</t>
+          <t>1.44536597007977</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>144.72</t>
+          <t>1.44715806081113</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>120.65</t>
+          <t>1.20654952659841</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>104.26</t>
+          <t>1.04264550385832</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-28.41</t>
+          <t>-0.28407231263883</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-26.82</t>
+          <t>-0.268194682004815</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-20.81</t>
+          <t>-0.208107076485677</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-21.01</t>
+          <t>-0.210080330282594</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.64</t>
+          <t>-0.13637487619784</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-0.0532996267035082</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.00792745831182162</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>0.0431036441357575</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>0.104642892423835</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>0.126588319251037</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>0.102145624944527</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>0.149834231619036</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>0.202965061822598</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>0.210314143709199</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>0.259177610422791</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>0.422023713093671</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>0.425335389811499</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>0.479972842668249</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>0.391161539685136</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>0.317935104070336</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>0.226018394105485</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>0.151408230204153</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>0.138502549310821</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>0.0817292523195483</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.0485738899230124</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.01032491125943</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.0453787040914893</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0100276313944025</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>0.0424476612625493</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>0.15241910898671</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-50.52</t>
+          <t>-0.505221985495827</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-47.93</t>
+          <t>-0.479292886155365</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-50.04</t>
+          <t>-0.50042334927147</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-51.15</t>
+          <t>-0.51149898496956</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-51.67</t>
+          <t>-0.516734340838724</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-50.53</t>
+          <t>-0.505278063656868</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-46.47</t>
+          <t>-0.464653606030711</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-44.36</t>
+          <t>-0.443606444113983</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-42.04</t>
+          <t>-0.420416463439253</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-36.8</t>
+          <t>-0.368018811425457</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-0.33222506861366</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-32.69</t>
+          <t>-0.32693700018043</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-0.263506223426034</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-26.75</t>
+          <t>-0.267470019929042</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-24.5</t>
+          <t>-0.244985088227323</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>0.314716592853654</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>0.289352273924789</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>0.471710312983246</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>0.384295539695831</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>26.99</t>
+          <t>0.269927484092942</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>0.297061559709093</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>0.224782722574218</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>0.208316064193756</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.0959776098369034</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>0.0841052906609325</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>0.104164674644756</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>0.127475797776474</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>0.272100163323524</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113588350277839</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>0.355611669451267</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>164.64</t>
+          <t>1.64638438220947</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>0.843777526035913</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>99.38</t>
+          <t>0.993801863163928</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>0.983901255003079</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>99.71</t>
+          <t>0.997106978555452</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>109.74</t>
+          <t>1.09741998812501</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>0.87666817619929</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>80.62</t>
+          <t>0.806241833211962</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>0.818761540928062</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>0.543342273360746</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.499539718200423</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>55.24</t>
+          <t>0.552433015311197</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>0.521095512203379</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>0.614190769684867</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>0.849107979739546</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-38.73</t>
+          <t>-0.387269136094274</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-33.25</t>
+          <t>-0.332526866694487</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-24.6</t>
+          <t>-0.245993050107969</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-25.7</t>
+          <t>-0.25698424983086</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-26.32</t>
+          <t>-0.263207149527119</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-30.06</t>
+          <t>-0.300610725790975</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-28.07</t>
+          <t>-0.280741209998827</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-29.1</t>
+          <t>-0.290969679541458</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-37.76</t>
+          <t>-0.37761592461423</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-0.372695604408537</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-35.33</t>
+          <t>-0.353302236675362</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-37.06</t>
+          <t>-0.370585839968471</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-38.33</t>
+          <t>-0.383270691950734</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-34.13</t>
+          <t>-0.341337019979827</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-31.16</t>
+          <t>-0.311629097339893</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-29.2</t>
+          <t>-0.292001345362834</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-27.03</t>
+          <t>-0.270283535287049</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-0.0297199706604946</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-0.119955157886286</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-0.128590243832522</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-0.0934661861907372</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-0.130145003336223</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-0.155945079691636</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-26.5</t>
+          <t>-0.265021097313891</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-0.270069432303552</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>-0.255204862725302</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-25.61</t>
+          <t>-0.256081912088005</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-25.8</t>
+          <t>-0.258036771176753</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-19.73</t>
+          <t>-0.197332783619071</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-0.115284297335865</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.0271795550366867</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>0.0428851337715552</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>0.248011404241801</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>0.163456769534929</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>0.113945351920066</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199557667313529</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>0.135085059052347</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.0851079354528532</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0617250255788868</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-0.0352136427154283</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-0.0333674599525097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.0366136309544622</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.0209217499550255</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.00892719821626708</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.128955540924341</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>181.74</t>
+          <t>1.81739322461828</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>162.34</t>
+          <t>1.6233887765711</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>152.44</t>
+          <t>1.52444108397248</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>131.51</t>
+          <t>1.31510950258558</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>129.41</t>
+          <t>1.2940762029901</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>97.08</t>
+          <t>0.970811116490688</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>104.24</t>
+          <t>1.0423772100195</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>0.669474336504772</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>0.48842975052722</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>0.408362751779326</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>55.62</t>
+          <t>0.556190519230745</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>0.610193926440728</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>63.82</t>
+          <t>0.638192894834783</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>52.41</t>
+          <t>0.524089857876369</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>62.21</t>
+          <t>0.622075799278968</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>0.108150333559031</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>0.0859706766995654</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>0.307138086395737</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.210478519906325</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>0.177878423134171</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.292207178454259</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>0.270888530075221</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25.31</t>
+          <t>0.253102802454486</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0.170143330681261</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>0.0646219510838297</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.0365814194201133</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.00150093003249585</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.00833989487453224</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0154083061026682</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0.0785290297999566</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-20.87</t>
+          <t>-0.208739492000611</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-0.210214711155693</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-0.043391216889045</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-13.2</t>
+          <t>-0.13198306305386</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-0.170030094210891</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-17.31</t>
+          <t>-0.173121358823848</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-21.35</t>
+          <t>-0.213471497592018</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-0.238563586054715</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-24.12</t>
+          <t>-0.241162723537704</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-29.5</t>
+          <t>-0.294994168613989</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-28.61</t>
+          <t>-0.286086424133528</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-25.56</t>
+          <t>-0.25561724023847</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-24.3</t>
+          <t>-0.242979783551395</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-21.14</t>
+          <t>-0.211411453343018</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-14.6</t>
+          <t>-0.145976271626264</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>0.0997637368741269</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>0.0687102815845855</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162408099288833</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.0675041844665896</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0270316231048722</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.0122560402938282</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-0.0476103097413171</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-0.0694434762968349</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-13.52</t>
+          <t>-0.135210768389715</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-0.180396755931168</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-0.172806903167457</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-0.169706282790076</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-0.135272718886244</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-0.0333950340514241</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>0.0809270389888617</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>54.56</t>
+          <t>0.545626658634859</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>0.483449189278847</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>0.494057259080913</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>0.554255732267369</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>0.472179324220149</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>0.403070325026011</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.429811188670591</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>0.268668684730765</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>0.301658758898478</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>0.294901700735119</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>0.341196529025031</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>0.393199115336014</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>0.329482890809513</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>0.311534565298447</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>0.288342544275092</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>46.11</t>
+          <t>0.461095025491653</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>0.50552815778018</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>0.594997163347184</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.56</t>
+          <t>0.615645122839923</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>0.552702176200661</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>54.61</t>
+          <t>0.546083024735859</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>0.600379961888335</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>0.467711315431181</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>54.58</t>
+          <t>0.545816505261953</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>0.606135544518735</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>0.623253917680473</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>0.726194625831772</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>66.05</t>
+          <t>0.660479955880166</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>0.837047726228666</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>1.03195926576722</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-0.0427990368012198</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>0.168874115198684</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>0.470935021236863</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>0.799477232600831</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>120.72</t>
+          <t>1.20718079792629</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>0.470553051655174</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>0.422143538241949</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>0.420768814376112</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>0.220509406209054</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>0.346577494032472</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-0.0450099978995199</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-0.078666952462494</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-20.65</t>
+          <t>-0.206514695355838</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-17.36</t>
+          <t>-0.173582162691058</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-0.203927845601936</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-0.558471798536298</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-51.27</t>
+          <t>-0.512738668294799</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-53.08</t>
+          <t>-0.53082587368765</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-53.72</t>
+          <t>-0.537166192979065</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-52.76</t>
+          <t>-0.52759598318667</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-52.76</t>
+          <t>-0.527574069577079</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-52.48</t>
+          <t>-0.524771765436046</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-49.61</t>
+          <t>-0.496114929568693</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-51.39</t>
+          <t>-0.513934255074674</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-52.06</t>
+          <t>-0.520604919866567</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-52.94</t>
+          <t>-0.529400296532294</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-0.53353927842419</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-49.93</t>
+          <t>-0.499337033304874</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-47.57</t>
+          <t>-0.475674292393668</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-49.23</t>
+          <t>-0.492304573815068</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>0.206209724589742</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>0.199072758912551</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>0.350596660756006</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>0.420305921680397</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>0.440487641630194</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>0.42245391888999</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>0.267787698240663</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>0.20542462276531</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>0.338106813981323</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>0.426868555486162</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>0.252594210826361</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>0.194043802556787</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>0.129056295740491</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>0.124873533063795</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0534073376673996</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-0.158302033698265</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-0.161258635156911</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-0.0963767917153336</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-8.82</t>
+          <t>-0.0881815802357376</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-0.0830809353704046</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-11.01</t>
+          <t>-0.110146628118624</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-0.100577773449784</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-0.0994906450403813</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-0.121381485904119</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-20.66</t>
+          <t>-0.206635563174032</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-17.17</t>
+          <t>-0.171724225367865</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-0.156291791883286</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-0.0716906271887402</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.0179560189553185</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>0.108141273688093</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-0.163564178445098</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.0463851555634286</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>0.0745005596307862</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>0.112388251416284</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>0.0530797045547242</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.0112595110995182</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.0234979855618853</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.0546245264840259</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.0517457020917376</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.0136745492560361</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.0162825103043313</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>0.0407521090453451</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0.153198180877085</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>0.182060597713208</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>0.130065060327831</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>0.102888041945791</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>0.150576528227607</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.280343773274637</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>0.448631599562988</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>0.52828749567508</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>0.469010782847079</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>0.445589996885508</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>0.487907933248531</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>0.40682154316995</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>0.42336186773556</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>0.388334905252529</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>0.349126131031146</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>0.383419623015692</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>0.509580426012997</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>0.587180397839265</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>134.88</t>
+          <t>1.34876028495879</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>122.53</t>
+          <t>1.22529309987436</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>123.87</t>
+          <t>1.23867522258171</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>79.83</t>
+          <t>0.798347496873841</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>0.699233873960681</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>0.755424770559499</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>80.12</t>
+          <t>0.801182174109812</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>72.45</t>
+          <t>0.7244988507624</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>66.82</t>
+          <t>0.668190449505005</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>0.899860781631209</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>0.89723624384138</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>0.847796269546887</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>102.21</t>
+          <t>1.02214520880191</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>0.907993969813637</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>96.04</t>
+          <t>0.960426346912001</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-0.121314668348648</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.00836211574274326</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>0.192633648327871</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>0.129083644569055</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.0285371623851896</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-0.0512102711215071</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.0345306318935261</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.0299074826873842</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.0029617618075698</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-0.0886392050433858</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-12.38</t>
+          <t>-0.123810291765075</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-0.106296621929007</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.0388882052484436</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-0.0640624301385991</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>0.12193145725893</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>153.41</t>
+          <t>1.53412694686488</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>146.12</t>
+          <t>1.4612075308994</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>145.06</t>
+          <t>1.45055303486581</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>1.3022597113364</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>123.17</t>
+          <t>1.23167338355443</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>153.22</t>
+          <t>1.53220817012261</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>160.95</t>
+          <t>1.60948667836419</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>168.01</t>
+          <t>1.6800935516586</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>168.85</t>
+          <t>1.6884938209207</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>156.76</t>
+          <t>1.56757591297444</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>150.73</t>
+          <t>1.50727152170497</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>135.89</t>
+          <t>1.35887037467056</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>109.27</t>
+          <t>1.09267495757852</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>80.33</t>
+          <t>0.803309810168213</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>0.970898089245207</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>104.37</t>
+          <t>1.04373436915713</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>1.18020018075485</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>135.02</t>
+          <t>1.35016644090712</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>112.19</t>
+          <t>1.12192175566101</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>99.29</t>
+          <t>0.992926204357255</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>0.944633679729643</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>77.63</t>
+          <t>0.776261494323864</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>0.799676507835968</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>79.09</t>
+          <t>0.790927993530145</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>0.885000131532769</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>115.85</t>
+          <t>1.15846240552237</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>117.05</t>
+          <t>1.17054127036445</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>124.56</t>
+          <t>1.24556513219986</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>131.18</t>
+          <t>1.31183732601856</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>131.67</t>
+          <t>1.31669979469557</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>0.295434434025132</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175810252142793</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>0.422310245758752</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>0.311946917468954</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>0.154656503494701</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.0851005691968418</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-0.188661547623496</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-0.105208646470692</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00190993827049524</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>0.0827479701903007</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>0.0369876438592789</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>0.0821590026915124</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.0148007951533777</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.000937995730677876</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>0.110364174988838</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-46.63</t>
+          <t>-0.466295027506888</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-0.427504553643671</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-0.177324371290126</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.66</t>
+          <t>-0.326572191786296</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-35.8</t>
+          <t>-0.357983384871075</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-34.28</t>
+          <t>-0.342833423713633</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-40.96</t>
+          <t>-0.40958585036264</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-0.471668779765102</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-42.18</t>
+          <t>-0.421838167038474</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-0.446434818105167</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-0.430389289912765</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-0.430425043919305</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-40.65</t>
+          <t>-0.406510543317969</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-43.89</t>
+          <t>-0.438943736990209</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-41.75</t>
+          <t>-0.417520647420971</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>0.0760367432392235</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.0366837892827878</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0268800686826449</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.0107788164533367</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>0.0947981057268239</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>0.148994105025637</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>0.432657322940689</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>0.476358266709085</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>69.52</t>
+          <t>0.695167317654489</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>0.701859355196604</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>66.92</t>
+          <t>0.669228479578636</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>0.736311205129055</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>73.38</t>
+          <t>0.7338399231583</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>0.717994849877883</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>0.958829307519001</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-23.05</t>
+          <t>-0.230451514189458</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-24.04</t>
+          <t>-0.240393921029213</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-13.88</t>
+          <t>-0.138794361385766</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-0.22941722243025</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-22.4</t>
+          <t>-0.223957640865512</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-0.232053828055052</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-25.34</t>
+          <t>-0.253354625601895</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-24.07</t>
+          <t>-0.240712009213373</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-0.0542456914054964</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-20.65</t>
+          <t>-0.206506419134473</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-19.2</t>
+          <t>-0.191961692470078</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-0.0575396673749311</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.011953712497808</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.0060186172176504</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.167045310305355</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>0.4410807414198</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.463003321606636</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>54.53</t>
+          <t>0.545271382947079</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>0.33151469171846</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.0134456231118674</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-0.0639448523668847</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-0.05881208187758</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>0.237196407478081</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>0.58019738723836</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>0.467378229205228</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>0.317830904945309</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>0.366947812414973</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>32.82</t>
+          <t>0.328152855609159</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>0.273777193457712</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>0.404591217598708</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>0.264165184061713</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.223140820984572</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>0.278505004598568</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>0.361952456770423</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>0.530975610915656</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>0.375412100876493</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>0.352883954283412</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27.71</t>
+          <t>0.277059303909459</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>0.150863368303861</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>0.121250270567734</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0556419255999898</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.0483674040004944</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-0.0565637049143126</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-0.211527017070876</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-0.238503288077704</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>241.73</t>
+          <t>2.41728347012472</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>202.95</t>
+          <t>2.02952500223063</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>220.75</t>
+          <t>2.20754128660058</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>223.16</t>
+          <t>2.23155399671611</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>230.41</t>
+          <t>2.30412015662692</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>2.15672323922897</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>216.88</t>
+          <t>2.16876545647291</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>225.77</t>
+          <t>2.25765147629297</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>192.86</t>
+          <t>1.92864124003648</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>121.46</t>
+          <t>1.21460181022041</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>1.18300219389495</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>104.99</t>
+          <t>1.04985339718662</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>83.25</t>
+          <t>0.832534267051643</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>0.882301513275188</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>58.17</t>
+          <t>0.58174590649511</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-18.4</t>
+          <t>-0.183999386591608</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-15.1</t>
+          <t>-0.150967802126089</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-0.039496144178945</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-0.0869227806571158</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-0.0658501381947286</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-0.0757095410337585</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-0.134673252186075</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-11.83</t>
+          <t>-0.118291900072386</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-0.175135090345304</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-11.76</t>
+          <t>-0.117611053748258</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-0.0719840622966144</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.0188000716200577</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0195560710723675</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-23.92</t>
+          <t>-0.23923672849874</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-22.52</t>
+          <t>-0.225237522401089</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00187422018462446</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.0176905484027334</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>0.140907973423963</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>0.0722296417293242</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>0.0637192687761332</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.01265888722604</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.0142666679850867</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-0.0359939474688956</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-0.0724954988469924</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-0.117427711592401</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-0.137879220311306</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>-0.122664391512374</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-13.15</t>
+          <t>-0.131450702456461</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-0.0354858540422014</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>0.106303933188275</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>0.251747434234259</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>0.143110035983698</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>0.1114949973865</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>0.125244918945815</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-0.0230481860989495</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>0.174307651087011</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>0.24430640608211</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>0.468125969492735</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>0.440820527738629</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>0.344995301637788</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>51.24</t>
+          <t>0.512392295025325</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>59.71</t>
+          <t>0.597061940821088</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>61.97</t>
+          <t>0.619703383289444</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-0.0338270558916146</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>0.0880444001128333</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>0.062695292159292</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.0142090738834881</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>0.132975317397294</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>0.193768000904363</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>0.230959601842029</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>0.171488493511917</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>0.157580013608353</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>0.200302856519808</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213570421239554</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>0.252932502849065</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>0.30228815754608</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>0.363582207248398</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>0.551435721679693</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>0.590676301699707</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>77.92</t>
+          <t>0.779240908231389</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>0.198336693127675</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.64</t>
+          <t>0.22641951990651</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>0.210655445746357</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>0.144930835761122</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>0.119104432990576</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.0195559142135252</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-0.0636201630721139</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-0.0830960461801383</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-0.11289798726459</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-0.139127177556245</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-0.139262760829738</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-0.122463645427489</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.0318033765025414</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0312577072332438</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0514857657437795</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-72.46</t>
+          <t>-0.724574771001668</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-70.94</t>
+          <t>-0.709421265919826</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-70.9</t>
+          <t>-0.709047451676042</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-71.5</t>
+          <t>-0.714964385330047</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-72.71</t>
+          <t>-0.727076022463283</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-72.22</t>
+          <t>-0.72220766808118</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-70.61</t>
+          <t>-0.706101972006724</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-70.49</t>
+          <t>-0.704893930892111</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-67.78</t>
+          <t>-0.67780630168317</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-65.51</t>
+          <t>-0.65512189221256</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-65.56</t>
+          <t>-0.655605105193312</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-64.79</t>
+          <t>-0.647893719479317</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>-60.7</t>
+          <t>-0.606981483730396</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>-0.574226139128131</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>-57.03</t>
+          <t>-0.570336954898273</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-42.89</t>
+          <t>-0.428909365432178</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-0.402741132375265</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-39.36</t>
+          <t>-0.393643993061613</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-40.13</t>
+          <t>-0.401285395846601</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-40.83</t>
+          <t>-0.408275693041674</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-42.28</t>
+          <t>-0.422830617962033</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-0.419794742631285</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-41.67</t>
+          <t>-0.416665611728695</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-40.87</t>
+          <t>-0.408743418160976</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-40.39</t>
+          <t>-0.403922000953609</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-40.59</t>
+          <t>-0.405852978552218</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-39.91</t>
+          <t>-0.399124959343047</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>-35.54</t>
+          <t>-0.355430516708956</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-32.94</t>
+          <t>-0.32937329488262</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>-32.83</t>
+          <t>-0.328277835459167</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
